--- a/app/static/xlsx-sample.xlsx
+++ b/app/static/xlsx-sample.xlsx
@@ -183,7 +183,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вебинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -213,7 +213,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Коллеги, всем привет! Я Дмитрий, на прошлой неделе мы проводили вебинар о сайтах для бизнеса. Если кому-то нужна запись — напишите, пришлю.</t>
+          <t xml:space="preserve">Коллеги, всем привет! Я Дмитрий, мы делаем сайты для малого бизнеса. Если кому-то нужен разбор вашего сайта — напишите, сделаю бесплатно.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -245,7 +245,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -275,7 +275,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Добрый день! Делимся конспектом семинара по продвижению в Telegram.</t>
+          <t xml:space="preserve">Добрый день! Делимся подборкой материалов по продвижению в Telegram.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -307,7 +307,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Курс</t>
+          <t xml:space="preserve">Клуб</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -364,7 +364,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вебинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -379,7 +379,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Анна, привет! Спасибо, что была на вебинаре. Как тебе тема с лендингами — актуально сейчас?</t>
+          <t xml:space="preserve">Анна, привет! Видел твой вопрос в группе про лендинги — актуально ещё?</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семинар</t>
+          <t xml:space="preserve">Клуб</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Борис, здравствуйте! Вы были на нашем семинаре — подскажите, удалось применить что-то из разобранного?</t>
+          <t xml:space="preserve">Борис, здравствуйте! Мы общались в клубе — подскажите, тема с сайтом ещё актуальна?</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вебинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вебинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семинар</t>
+          <t xml:space="preserve">Клуб</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Курс</t>
+          <t xml:space="preserve">Клуб</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вебинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Всем привет! Анонс нового вебинара.</t>
+          <t xml:space="preserve">Всем привет! Поделюсь чек-листом для сайта, кому интересно.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вебинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вебинар</t>
+          <t xml:space="preserve">Сообщество</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Имя], привет! Спасибо, что пришли на вебинар.</t>
+          <t xml:space="preserve">[Имя], привет! Рад знакомству в нашей группе.</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">После вебинара</t>
+          <t xml:space="preserve">Предложение</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Имя], добрый день! Вы были на нашем вебинаре о сайтах — остались ли вопросы? Могу прислать запись и презентацию.</t>
+          <t xml:space="preserve">[Имя], добрый день! Мы делаем сайты для малого бизнеса — остались ли вопросы по вашему сайту? Могу прислать примеры работ.</t>
         </is>
       </c>
     </row>
